--- a/vault-dalarna-university/04 ISLL/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Nedlagda kursreferenser.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens; rad: - Didaktik och ledarskap för ämneslärare, 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens; rad: - Didaktik och ledarskap för ämneslärare, 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens; rad: - Text, kommunikation och lärande i en mångkulturell skola, 15 hp</t>
+          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens; rad: - Text, kommunikation och lärande i en mångkulturell skola, 15 hp</t>
+          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">

--- a/vault-dalarna-university/04 ISLL/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -509,15 +531,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -536,15 +568,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
@@ -563,31 +601,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Programmet listar nedlagd kurs</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Nedlagda kursreferenser.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Nedlagda kursreferenser" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nedlagda kursreferenser'!$A$1:$H$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -512,7 +518,12 @@
           <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LG79A</t>
         </is>
@@ -549,7 +560,12 @@
           <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>`PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LGGYA</t>
         </is>
@@ -582,7 +598,12 @@
           <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>`GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLF3A</t>
         </is>
@@ -615,23 +636,28 @@
           <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>`GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LLL3A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:H5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Nedlagda kursreferenser.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Nedlagda kursreferenser.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+          <t>`Didaktik och ledarskap för ämneslärare`</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare` → `PG1020` (nedlagd 2018-07-02) — plain-text-referens</t>
+          <t>`Didaktik och ledarskap för ämneslärare`</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+          <t>`Text, kommunikation och lärande i en mångkulturell skola`</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Text, kommunikation och lärande i en mångkulturell skola` → `GSV22L` (nedlagd 2024-10-11) — plain-text-referens</t>
+          <t>`Text, kommunikation och lärande i en mångkulturell skola`</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
